--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_3865_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_3865_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R048f5b15bf694edc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1d3e2daa026c466a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2421 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1280</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0590</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0640</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3770</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8530</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/04/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3940</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/03/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/03/2026</x:t>
         </x:is>
       </x:c>
